--- a/results/02_taxa_assemblage/LDA_Method/ModelFinalized/tables/site_plot_data.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelFinalized/tables/site_plot_data.xlsx
@@ -481,11 +481,11 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>1.760459261603462</v>
@@ -504,16 +504,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1.085939220724867</v>
@@ -557,11 +557,11 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0.6348874980322061</v>
@@ -631,7 +631,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -656,16 +656,16 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0952502001652358</v>
@@ -685,11 +685,11 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>-1.230447533763279</v>
@@ -709,11 +709,11 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>-1.268429965647923</v>
@@ -733,11 +733,11 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0.3327897274546787</v>
@@ -757,11 +757,11 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>0.4143362638611745</v>
@@ -809,11 +809,11 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>-0.731163039793023</v>
@@ -857,11 +857,11 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>-0.367699053603147</v>
@@ -953,11 +953,11 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3071254310082703</v>
@@ -1128,16 +1128,16 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
         <v>1.497152431809525</v>
@@ -1157,11 +1157,11 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
         <v>2.224350406884099</v>
@@ -1208,7 +1208,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>2</v>
@@ -1217,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>1.231324147092851</v>
@@ -1261,11 +1261,11 @@
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
         <v>-1.025662827026679</v>
@@ -1429,11 +1429,11 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
         <v>0.8836670497663567</v>
@@ -1604,16 +1604,16 @@
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
         <v>-1.692695171493578</v>
@@ -1633,11 +1633,11 @@
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
         <v>-1.337713790404915</v>
@@ -1656,16 +1656,16 @@
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49" t="b">
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
         <v>-1.594076758658212</v>
@@ -1685,11 +1685,11 @@
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
         <v>-1.404255595847981</v>
@@ -1708,16 +1708,16 @@
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
         <v>0.184728986161671</v>
@@ -1737,11 +1737,11 @@
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>-1.999914889174814</v>
@@ -1761,11 +1761,11 @@
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>-1.6117988085944</v>
@@ -1813,11 +1813,11 @@
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
         <v>-1.196567122928959</v>
@@ -1865,11 +1865,11 @@
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
         <v>-1.457357361954873</v>
@@ -1889,11 +1889,11 @@
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
         <v>0.06931888684034995</v>
@@ -1913,11 +1913,11 @@
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
         <v>-1.565713443734886</v>
@@ -1937,11 +1937,11 @@
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
         <v>0.4958354836775877</v>
@@ -1961,11 +1961,11 @@
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
         <v>-1.248183987559397</v>
@@ -1985,11 +1985,11 @@
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
         <v>-1.629344930425405</v>
@@ -2033,11 +2033,11 @@
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
         <v>-0.8666454775891798</v>
@@ -2249,11 +2249,11 @@
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
         <v>-0.7226046072613844</v>
@@ -2297,11 +2297,11 @@
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
         <v>-0.3763606133978886</v>
@@ -2397,11 +2397,11 @@
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
         <v>-0.7189652708238128</v>
@@ -2421,11 +2421,11 @@
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
         <v>0.4798310722172192</v>
@@ -2493,11 +2493,11 @@
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
         <v>-1.247032889555265</v>
@@ -2565,11 +2565,11 @@
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G86" t="n">
         <v>0.725980439622903</v>
@@ -2589,11 +2589,11 @@
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
         <v>-0.946704198945496</v>
@@ -2613,11 +2613,11 @@
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
         <v>-0.9989848786498587</v>
@@ -2637,11 +2637,11 @@
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
         <v>-1.215905235012254</v>
@@ -2661,11 +2661,11 @@
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
         <v>-1.417173286113156</v>
@@ -2684,16 +2684,16 @@
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
       </c>
       <c r="E91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G91" t="n">
         <v>0.1719008394752966</v>
@@ -2761,11 +2761,11 @@
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
         <v>0.6510316082800551</v>
@@ -2785,11 +2785,11 @@
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
         <v>-1.150985881579185</v>
@@ -2833,11 +2833,11 @@
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
         <v>0.937394931562584</v>
@@ -2857,11 +2857,11 @@
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
         <v>0.9522750529103752</v>
@@ -2961,11 +2961,11 @@
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G102" t="n">
         <v>0.03807955786515318</v>
@@ -2985,11 +2985,11 @@
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G103" t="n">
         <v>-0.1611338745056887</v>
@@ -3133,11 +3133,11 @@
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G109" t="n">
         <v>-1.137861568920309</v>
@@ -3157,11 +3157,11 @@
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G110" t="n">
         <v>-0.9481149886558807</v>
@@ -3204,16 +3204,16 @@
         <v>1</v>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" t="b">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
         <v>3</v>
-      </c>
-      <c r="E112" t="b">
-        <v>0</v>
-      </c>
-      <c r="F112" t="n">
-        <v>1</v>
       </c>
       <c r="G112" t="n">
         <v>-0.5836465725462537</v>
@@ -3257,11 +3257,11 @@
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G114" t="n">
         <v>-0.8396837594067276</v>
@@ -3281,11 +3281,11 @@
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G115" t="n">
         <v>-1.215931307913357</v>
@@ -3329,11 +3329,11 @@
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G117" t="n">
         <v>-0.8136753824243101</v>
@@ -3355,10 +3355,10 @@
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
@@ -3405,11 +3405,11 @@
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
         <v>-0.5634214294000531</v>
@@ -3429,11 +3429,11 @@
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
         <v>-0.9372917639956571</v>
@@ -3477,11 +3477,11 @@
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G123" t="n">
         <v>-0.1337164747089373</v>
@@ -3501,11 +3501,11 @@
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G124" t="n">
         <v>0.1100906591718397</v>
@@ -3525,11 +3525,11 @@
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G125" t="n">
         <v>-0.7179928884722595</v>
@@ -3549,11 +3549,11 @@
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
         <v>-2.679269731680175</v>
@@ -3573,11 +3573,11 @@
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G127" t="n">
         <v>0.2765155769125489</v>
@@ -3597,11 +3597,11 @@
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G128" t="n">
         <v>-1.398017493668135</v>
@@ -3621,11 +3621,11 @@
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G129" t="n">
         <v>-0.5120266057745779</v>
@@ -3645,11 +3645,11 @@
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
         <v>-0.8308891455401692</v>
@@ -3669,11 +3669,11 @@
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G131" t="n">
         <v>-0.7270424334232468</v>
@@ -3717,11 +3717,11 @@
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G133" t="n">
         <v>-0.9965114403039921</v>
@@ -3741,11 +3741,11 @@
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G134" t="n">
         <v>-0.7810323591180083</v>
@@ -3789,11 +3789,11 @@
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G136" t="n">
         <v>-0.8383674869864858</v>
@@ -3813,11 +3813,11 @@
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G137" t="n">
         <v>0.1098385008120663</v>
@@ -3837,11 +3837,11 @@
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G138" t="n">
         <v>-1.087925275322582</v>
@@ -3861,11 +3861,11 @@
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
         <v>-0.6246046587468299</v>
@@ -3885,11 +3885,11 @@
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G140" t="n">
         <v>-0.8458566616939242</v>
@@ -3909,11 +3909,11 @@
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
         <v>-2.389935285382684</v>
@@ -3933,11 +3933,11 @@
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G142" t="n">
         <v>-1.089589851598733</v>
@@ -3957,11 +3957,11 @@
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
         <v>0.1756716270923005</v>
@@ -4009,11 +4009,11 @@
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G145" t="n">
         <v>-1.098343697747283</v>
@@ -4032,16 +4032,16 @@
         <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E146" t="b">
         <v>1</v>
       </c>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G146" t="n">
         <v>-0.139485385356923</v>
@@ -4089,11 +4089,11 @@
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G148" t="n">
         <v>-0.3456189527205129</v>
@@ -4113,11 +4113,11 @@
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G149" t="n">
         <v>0.8201540273188695</v>
@@ -4209,11 +4209,11 @@
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G153" t="n">
         <v>0.6325557657442994</v>
@@ -4233,11 +4233,11 @@
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G154" t="n">
         <v>0.1153993507840051</v>
@@ -4257,11 +4257,11 @@
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G155" t="n">
         <v>-0.7536201089289365</v>
@@ -4281,11 +4281,11 @@
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G156" t="n">
         <v>0.007240738182834323</v>
@@ -4331,10 +4331,10 @@
         <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F158" t="n">
         <v>1</v>
@@ -4357,11 +4357,11 @@
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G159" t="n">
         <v>1.355060870728787</v>
@@ -4381,11 +4381,11 @@
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G160" t="n">
         <v>-0.3425388682196279</v>
@@ -4407,10 +4407,10 @@
         <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161" t="n">
         <v>1</v>
@@ -4433,11 +4433,11 @@
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G162" t="n">
         <v>-0.1192457301075725</v>
@@ -4456,16 +4456,16 @@
         <v>1</v>
       </c>
       <c r="C163" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D163" t="n">
         <v>1</v>
       </c>
       <c r="E163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G163" t="n">
         <v>-0.378460757545615</v>
@@ -4565,11 +4565,11 @@
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G167" t="n">
         <v>-0.3698453355041255</v>
@@ -4589,11 +4589,11 @@
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G168" t="n">
         <v>-1.013449452795223</v>
@@ -4640,7 +4640,7 @@
         <v>1</v>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D170" t="n">
         <v>1</v>
@@ -4649,7 +4649,7 @@
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G170" t="n">
         <v>-1.166708458932659</v>
@@ -4669,11 +4669,11 @@
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G171" t="n">
         <v>-0.2798833086439018</v>
@@ -4692,16 +4692,16 @@
         <v>1</v>
       </c>
       <c r="C172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E172" t="b">
         <v>1</v>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G172" t="n">
         <v>-1.108328995561727</v>
@@ -4720,16 +4720,16 @@
         <v>1</v>
       </c>
       <c r="C173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D173" t="n">
         <v>1</v>
       </c>
       <c r="E173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G173" t="n">
         <v>-0.8989315202919811</v>
@@ -4748,16 +4748,16 @@
         <v>1</v>
       </c>
       <c r="C174" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D174" t="n">
         <v>1</v>
       </c>
       <c r="E174" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G174" t="n">
         <v>-0.8289590100749287</v>
@@ -4776,16 +4776,16 @@
         <v>1</v>
       </c>
       <c r="C175" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D175" t="n">
         <v>1</v>
       </c>
       <c r="E175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G175" t="n">
         <v>-0.7602840750786108</v>
@@ -4805,11 +4805,11 @@
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G176" t="n">
         <v>0.1603806362814416</v>
@@ -4829,11 +4829,11 @@
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G177" t="n">
         <v>0.2026146551303367</v>
@@ -4853,11 +4853,11 @@
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G178" t="n">
         <v>0.4479711659430992</v>
@@ -4877,11 +4877,11 @@
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G179" t="n">
         <v>-1.27964735379897</v>
@@ -4901,11 +4901,11 @@
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G180" t="n">
         <v>-1.143942787547049</v>
@@ -4949,11 +4949,11 @@
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G182" t="n">
         <v>-0.740698573694984</v>
@@ -4973,11 +4973,11 @@
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G183" t="n">
         <v>-1.86200958315026</v>
@@ -4997,11 +4997,11 @@
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G184" t="n">
         <v>-0.3987772645814109</v>
@@ -5021,11 +5021,11 @@
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G185" t="n">
         <v>-0.05345155911196149</v>
@@ -5045,11 +5045,11 @@
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G186" t="n">
         <v>-0.07683962053629081</v>
@@ -5092,16 +5092,16 @@
         <v>1</v>
       </c>
       <c r="C188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E188" t="b">
         <v>1</v>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G188" t="n">
         <v>-0.8145098685722081</v>
@@ -5148,16 +5148,16 @@
         <v>1</v>
       </c>
       <c r="C190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D190" t="n">
+        <v>1</v>
+      </c>
+      <c r="E190" t="b">
+        <v>0</v>
+      </c>
+      <c r="F190" t="n">
         <v>3</v>
-      </c>
-      <c r="E190" t="b">
-        <v>0</v>
-      </c>
-      <c r="F190" t="n">
-        <v>2</v>
       </c>
       <c r="G190" t="n">
         <v>-0.1981338110111849</v>
@@ -5179,10 +5179,10 @@
         <v>1</v>
       </c>
       <c r="D191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F191" t="n">
         <v>1</v>
@@ -5204,16 +5204,16 @@
         <v>1</v>
       </c>
       <c r="C192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D192" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" t="b">
+        <v>0</v>
+      </c>
+      <c r="F192" t="n">
         <v>3</v>
-      </c>
-      <c r="E192" t="b">
-        <v>0</v>
-      </c>
-      <c r="F192" t="n">
-        <v>2</v>
       </c>
       <c r="G192" t="n">
         <v>-0.2481570869328451</v>
@@ -5233,11 +5233,11 @@
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G193" t="n">
         <v>-0.3539561828061074</v>
@@ -5257,11 +5257,11 @@
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G194" t="n">
         <v>0.03579650184533321</v>
@@ -5281,11 +5281,11 @@
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G195" t="n">
         <v>-0.3904733115518739</v>
@@ -5305,11 +5305,11 @@
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G196" t="n">
         <v>0.3959831139048317</v>
@@ -5329,11 +5329,11 @@
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G197" t="n">
         <v>-0.3888140512869609</v>
@@ -5353,11 +5353,11 @@
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G198" t="n">
         <v>-0.6801278881941628</v>
@@ -5377,11 +5377,11 @@
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G199" t="n">
         <v>-0.4538005434840531</v>
@@ -5401,11 +5401,11 @@
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G200" t="n">
         <v>0.0400682187433524</v>
@@ -5425,11 +5425,11 @@
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G201" t="n">
         <v>0.4675041812044795</v>
@@ -5501,11 +5501,11 @@
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G204" t="n">
         <v>-1.130628774951365</v>
@@ -5525,11 +5525,11 @@
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G205" t="n">
         <v>-0.858943728729073</v>
@@ -5549,11 +5549,11 @@
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G206" t="n">
         <v>-0.836057260149892</v>
@@ -5572,16 +5572,16 @@
         <v>1</v>
       </c>
       <c r="C207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D207" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" t="b">
+        <v>0</v>
+      </c>
+      <c r="F207" t="n">
         <v>3</v>
-      </c>
-      <c r="E207" t="b">
-        <v>0</v>
-      </c>
-      <c r="F207" t="n">
-        <v>1</v>
       </c>
       <c r="G207" t="n">
         <v>-1.593504621171649</v>
@@ -5603,10 +5603,10 @@
         <v>3</v>
       </c>
       <c r="D208" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F208" t="n">
         <v>3</v>
@@ -5628,16 +5628,16 @@
         <v>1</v>
       </c>
       <c r="C209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D209" t="n">
+        <v>1</v>
+      </c>
+      <c r="E209" t="b">
+        <v>0</v>
+      </c>
+      <c r="F209" t="n">
         <v>3</v>
-      </c>
-      <c r="E209" t="b">
-        <v>0</v>
-      </c>
-      <c r="F209" t="n">
-        <v>2</v>
       </c>
       <c r="G209" t="n">
         <v>-0.5997916110866084</v>
@@ -5656,16 +5656,16 @@
         <v>1</v>
       </c>
       <c r="C210" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D210" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" t="b">
+        <v>0</v>
+      </c>
+      <c r="F210" t="n">
         <v>3</v>
-      </c>
-      <c r="E210" t="b">
-        <v>0</v>
-      </c>
-      <c r="F210" t="n">
-        <v>1</v>
       </c>
       <c r="G210" t="n">
         <v>-0.2198195753894135</v>
@@ -5685,11 +5685,11 @@
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G211" t="n">
         <v>-0.2640472235311542</v>
@@ -5708,16 +5708,16 @@
         <v>1</v>
       </c>
       <c r="C212" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D212" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E212" t="b">
         <v>1</v>
       </c>
       <c r="F212" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G212" t="n">
         <v>0.2550027031157554</v>
@@ -5765,11 +5765,11 @@
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G214" t="n">
         <v>0.6004218807183793</v>
@@ -5788,16 +5788,16 @@
         <v>1</v>
       </c>
       <c r="C215" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D215" t="n">
         <v>1</v>
       </c>
       <c r="E215" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F215" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G215" t="n">
         <v>1.481298200754268</v>
@@ -5865,11 +5865,11 @@
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G218" t="n">
         <v>-0.02655415116838269</v>
@@ -5889,11 +5889,11 @@
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G219" t="n">
         <v>0.1623579943907998</v>
@@ -5937,11 +5937,11 @@
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G221" t="n">
         <v>0.4128965206102206</v>
@@ -5961,11 +5961,11 @@
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G222" t="n">
         <v>0.0960077991113934</v>
@@ -6009,11 +6009,11 @@
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G224" t="n">
         <v>0.1867277206334193</v>
@@ -6033,11 +6033,11 @@
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G225" t="n">
         <v>-0.5450984271941114</v>
@@ -6129,11 +6129,11 @@
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G229" t="n">
         <v>-1.554261942046767</v>
@@ -6153,11 +6153,11 @@
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G230" t="n">
         <v>0.8620026481151176</v>
@@ -6177,11 +6177,11 @@
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G231" t="n">
         <v>-1.899162021735144</v>
@@ -6201,11 +6201,11 @@
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G232" t="n">
         <v>-1.63553129634541</v>
@@ -6225,11 +6225,11 @@
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G233" t="n">
         <v>-0.1745709921678751</v>
@@ -6249,11 +6249,11 @@
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G234" t="n">
         <v>-1.743287985342949</v>
